--- a/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_PYRAD/results.xlsx
+++ b/mlef_pipeline/results/OS_6/SQUAMOUS/RWD_PYRAD/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.65 ± 0.08</t>
+          <t>0.67 ± 0.08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.51 ± 0.08</t>
+          <t>0.60 ± 0.08</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.64 ± 0.28</t>
+          <t>0.66 ± 0.17</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.53 ± 0.35</t>
+          <t>0.59 ± 0.15</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.54 ± 0.24</t>
+          <t>0.58 ± 0.24</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,22 +528,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.56 ± 0.44</t>
+          <t>0.62 ± 0.41</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="F4" t="n">
